--- a/запас словарей/rust.xlsx
+++ b/запас словарей/rust.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\запас словарей\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDC2B21E-0796-4A68-A3E2-8C3DDABAA1AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA2F6753-0C53-48D8-B491-516154890B80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-25710" yWindow="2110" windowWidth="25820" windowHeight="10300" xr2:uid="{FA5CFF00-0E27-4D86-8392-510BBAD6F7FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="Лист2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="340">
   <si>
     <t>Nightly rust</t>
   </si>
@@ -237,13 +238,881 @@
   </si>
   <si>
     <t>вызывающей рукописи</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В чрезвычайном случае </t>
+  </si>
+  <si>
+    <t>В чрезвычайной случая</t>
+  </si>
+  <si>
+    <t>этот случай</t>
+  </si>
+  <si>
+    <t>эту случай</t>
+  </si>
+  <si>
+    <t>данный мгновение</t>
+  </si>
+  <si>
+    <t>данное мгновение</t>
+  </si>
+  <si>
+    <t>текущий мгновение</t>
+  </si>
+  <si>
+    <t>текущее мгновение</t>
+  </si>
+  <si>
+    <t>одну действие</t>
+  </si>
+  <si>
+    <t>одно действие</t>
+  </si>
+  <si>
+    <t>Этот дополнение</t>
+  </si>
+  <si>
+    <t>Это дополнение</t>
+  </si>
+  <si>
+    <t>эта руководство</t>
+  </si>
+  <si>
+    <t>это руководство</t>
+  </si>
+  <si>
+    <t>ход мыслей, которая</t>
+  </si>
+  <si>
+    <t>ход мыслей, который</t>
+  </si>
+  <si>
+    <t>вся ход мыслей</t>
+  </si>
+  <si>
+    <t>весь ход мыслей</t>
+  </si>
+  <si>
+    <t>ход мыслей, которую</t>
+  </si>
+  <si>
+    <t>с этой сведениями</t>
+  </si>
+  <si>
+    <t>с этими сведениями</t>
+  </si>
+  <si>
+    <t>правильная преобразование</t>
+  </si>
+  <si>
+    <t>правильное преобразование</t>
+  </si>
+  <si>
+    <t>в выполнения</t>
+  </si>
+  <si>
+    <t>в выполнении</t>
+  </si>
+  <si>
+    <t>вызывающему рукописи</t>
+  </si>
+  <si>
+    <t>определённую ход мыслей</t>
+  </si>
+  <si>
+    <t>определённый ход мыслей</t>
+  </si>
+  <si>
+    <t>приведён рукопись</t>
+  </si>
+  <si>
+    <t>приведена рукопись</t>
+  </si>
+  <si>
+    <t>Эта ярлык</t>
+  </si>
+  <si>
+    <t>Этот ярлык</t>
+  </si>
+  <si>
+    <t>добавлен рукопись</t>
+  </si>
+  <si>
+    <t>добавлена рукопись</t>
+  </si>
+  <si>
+    <t>определён второе</t>
+  </si>
+  <si>
+    <t>определено второе</t>
+  </si>
+  <si>
+    <t>допустимым рукописью</t>
+  </si>
+  <si>
+    <t>допустимой рукописью</t>
+  </si>
+  <si>
+    <t>В встроенной</t>
+  </si>
+  <si>
+    <t>Во встроенной</t>
+  </si>
+  <si>
+    <t>необходимую преобразование</t>
+  </si>
+  <si>
+    <t>необходимое преобразование</t>
+  </si>
+  <si>
+    <t>равнозначным рукописи</t>
+  </si>
+  <si>
+    <t>равнозначной рукописи</t>
+  </si>
+  <si>
+    <t>к ярлыке</t>
+  </si>
+  <si>
+    <t>к ярлыку</t>
+  </si>
+  <si>
+    <t>чья ярлык</t>
+  </si>
+  <si>
+    <t>чей ярлык</t>
+  </si>
+  <si>
+    <t>второй свойство</t>
+  </si>
+  <si>
+    <t>второе свойство</t>
+  </si>
+  <si>
+    <t>данная выполнение</t>
+  </si>
+  <si>
+    <t>данное выполнение</t>
+  </si>
+  <si>
+    <t>более производительна</t>
+  </si>
+  <si>
+    <t>более производительно</t>
+  </si>
+  <si>
+    <t>ни один из его свойств</t>
+  </si>
+  <si>
+    <t>ни одно из его свойств</t>
+  </si>
+  <si>
+    <t>неверный рукопись</t>
+  </si>
+  <si>
+    <t>неверная рукопись</t>
+  </si>
+  <si>
+    <t>повторение завершена</t>
+  </si>
+  <si>
+    <t>повторение завершено</t>
+  </si>
+  <si>
+    <t>был бы возможность</t>
+  </si>
+  <si>
+    <t>была бы возможность</t>
+  </si>
+  <si>
+    <t>старый исполнение</t>
+  </si>
+  <si>
+    <t>старое исполнение</t>
+  </si>
+  <si>
+    <t>любым рукописью</t>
+  </si>
+  <si>
+    <t>любой рукописью</t>
+  </si>
+  <si>
+    <t>важный мгновение</t>
+  </si>
+  <si>
+    <t>важное мгновение</t>
+  </si>
+  <si>
+    <t>из приложении</t>
+  </si>
+  <si>
+    <t>из приложения</t>
+  </si>
+  <si>
+    <t>создаём папка</t>
+  </si>
+  <si>
+    <t>создаём папку</t>
+  </si>
+  <si>
+    <t>создаем папка</t>
+  </si>
+  <si>
+    <t>создаем папку</t>
+  </si>
+  <si>
+    <t>в отдельный папка</t>
+  </si>
+  <si>
+    <t>в отдельную папку</t>
+  </si>
+  <si>
+    <t>текущий рабочий папка</t>
+  </si>
+  <si>
+    <t>текущая рабочая папка</t>
+  </si>
+  <si>
+    <t>обрабатывает папка</t>
+  </si>
+  <si>
+    <t>обрабатывает папку</t>
+  </si>
+  <si>
+    <t>создайте папка</t>
+  </si>
+  <si>
+    <t>создайте папку</t>
+  </si>
+  <si>
+    <t>один папка</t>
+  </si>
+  <si>
+    <t>одна папка</t>
+  </si>
+  <si>
+    <t>свой собственный папка</t>
+  </si>
+  <si>
+    <t>свою собственную папку</t>
+  </si>
+  <si>
+    <t>из папка</t>
+  </si>
+  <si>
+    <t>из папки</t>
+  </si>
+  <si>
+    <t>две указания</t>
+  </si>
+  <si>
+    <t>два указания</t>
+  </si>
+  <si>
+    <t>одинаковым приставкой</t>
+  </si>
+  <si>
+    <t>одинаковой приставкой</t>
+  </si>
+  <si>
+    <t>в одной указания</t>
+  </si>
+  <si>
+    <t>в одном указании</t>
+  </si>
+  <si>
+    <t>одну указанию</t>
+  </si>
+  <si>
+    <t>одно указание</t>
+  </si>
+  <si>
+    <t>эта указание</t>
+  </si>
+  <si>
+    <t>это указание</t>
+  </si>
+  <si>
+    <t>лучшие опытов</t>
+  </si>
+  <si>
+    <t>лучшие опыты</t>
+  </si>
+  <si>
+    <t>рукописью, написанным</t>
+  </si>
+  <si>
+    <t>рукописью, написанной</t>
+  </si>
+  <si>
+    <t>Данная стопки</t>
+  </si>
+  <si>
+    <t>Данная стопка</t>
+  </si>
+  <si>
+    <t>Иная выполнение</t>
+  </si>
+  <si>
+    <t>Иное выполнение</t>
+  </si>
+  <si>
+    <t>обнародованную размещение</t>
+  </si>
+  <si>
+    <t>обнародованное размещение</t>
+  </si>
+  <si>
+    <t>условной выполнения</t>
+  </si>
+  <si>
+    <t>условного выполнения</t>
+  </si>
+  <si>
+    <t>во второй указания</t>
+  </si>
+  <si>
+    <t>во втором указании</t>
+  </si>
+  <si>
+    <t>внешний дополнение</t>
+  </si>
+  <si>
+    <t>внешнее дополнение</t>
+  </si>
+  <si>
+    <t>одновременную изменение</t>
+  </si>
+  <si>
+    <t>одновременное изменение</t>
+  </si>
+  <si>
+    <t>в корне устройство</t>
+  </si>
+  <si>
+    <t>в корне устройства</t>
+  </si>
+  <si>
+    <t>мы используется</t>
+  </si>
+  <si>
+    <t>мы используем</t>
+  </si>
+  <si>
+    <t>с такой же устройством</t>
+  </si>
+  <si>
+    <t>с таким же устройством</t>
+  </si>
+  <si>
+    <t>рукописью использующим</t>
+  </si>
+  <si>
+    <t>рукописью использующей</t>
+  </si>
+  <si>
+    <t>он ещё не собирается</t>
+  </si>
+  <si>
+    <t>она ещё не собирается</t>
+  </si>
+  <si>
+    <t>видеть среда</t>
+  </si>
+  <si>
+    <t>видеть среду</t>
+  </si>
+  <si>
+    <t>внутреннего рукописи</t>
+  </si>
+  <si>
+    <t>внутренней рукописи</t>
+  </si>
+  <si>
+    <t>внешнего рукописи</t>
+  </si>
+  <si>
+    <t>внешней рукописи</t>
+  </si>
+  <si>
+    <t>ход мыслей такая же</t>
+  </si>
+  <si>
+    <t>ход мыслей такой же</t>
+  </si>
+  <si>
+    <t>согласованном рукописи</t>
+  </si>
+  <si>
+    <t>такого согласования рукописи</t>
+  </si>
+  <si>
+    <t>такой согласования рукописи</t>
+  </si>
+  <si>
+    <t>через проверку</t>
+  </si>
+  <si>
+    <t>через проверка</t>
+  </si>
+  <si>
+    <t>Данное изложение</t>
+  </si>
+  <si>
+    <t>Данная изложение</t>
+  </si>
+  <si>
+    <t>объединенной рукописи</t>
+  </si>
+  <si>
+    <t>объединенном рукописи</t>
+  </si>
+  <si>
+    <t>на согласовании рукописи</t>
+  </si>
+  <si>
+    <t>на согласования рукописи</t>
+  </si>
+  <si>
+    <t>связанной рукописи</t>
+  </si>
+  <si>
+    <t>связанного рукописи</t>
+  </si>
+  <si>
+    <t>рукописи, найденной</t>
+  </si>
+  <si>
+    <t>рукописи, найденном</t>
+  </si>
+  <si>
+    <t>первые части состоящие</t>
+  </si>
+  <si>
+    <t>первые части состоящей</t>
+  </si>
+  <si>
+    <t>тот же ход мыслей</t>
+  </si>
+  <si>
+    <t>ту же ход мыслей</t>
+  </si>
+  <si>
+    <t>своей рукописи</t>
+  </si>
+  <si>
+    <t>своего рукописи</t>
+  </si>
+  <si>
+    <t>дополнение, содержащее</t>
+  </si>
+  <si>
+    <t>дополнение, содержащий</t>
+  </si>
+  <si>
+    <t>набор возможностей</t>
+  </si>
+  <si>
+    <t>набор возможности</t>
+  </si>
+  <si>
+    <t>корневой раздел</t>
+  </si>
+  <si>
+    <t>корневое раздел</t>
+  </si>
+  <si>
+    <t>общим подходом</t>
+  </si>
+  <si>
+    <t>общей подходом</t>
+  </si>
+  <si>
+    <t>с исходной рукописью</t>
+  </si>
+  <si>
+    <t>с исходным рукописью</t>
+  </si>
+  <si>
+    <t>среда в которой</t>
+  </si>
+  <si>
+    <t>среда в котором</t>
+  </si>
+  <si>
+    <t>с разделами</t>
+  </si>
+  <si>
+    <t>со разделами</t>
+  </si>
+  <si>
+    <t>корневое звено</t>
+  </si>
+  <si>
+    <t>корневой звено</t>
+  </si>
+  <si>
+    <t>неиспользованной рукописью</t>
+  </si>
+  <si>
+    <t>неиспользованным рукописью</t>
+  </si>
+  <si>
+    <t>Рукопись собралась</t>
+  </si>
+  <si>
+    <t>Рукопись собрался</t>
+  </si>
+  <si>
+    <t>какая-либо рукописи</t>
+  </si>
+  <si>
+    <t>какой-либо рукописи</t>
+  </si>
+  <si>
+    <t>сторонней рукописи</t>
+  </si>
+  <si>
+    <t>стороннего рукописи</t>
+  </si>
+  <si>
+    <t>Такое создание</t>
+  </si>
+  <si>
+    <t>Такая создание</t>
+  </si>
+  <si>
+    <t>в этой же папке</t>
+  </si>
+  <si>
+    <t>в этой же папки</t>
+  </si>
+  <si>
+    <t>выполняемое
+дело</t>
+  </si>
+  <si>
+    <t>выполняемый дело</t>
+  </si>
+  <si>
+    <t>Пренебрегаем
+ими</t>
+  </si>
+  <si>
+    <t>Пренебрегаем их</t>
+  </si>
+  <si>
+    <t>Разумное создание</t>
+  </si>
+  <si>
+    <t>Разумная создание</t>
+  </si>
+  <si>
+    <t>такое устройство</t>
+  </si>
+  <si>
+    <t>такую устройство</t>
+  </si>
+  <si>
+    <t>данные возможности</t>
+  </si>
+  <si>
+    <t>данную возможности</t>
+  </si>
+  <si>
+    <t>в последующих разделах</t>
+  </si>
+  <si>
+    <t>в последующей разделы</t>
+  </si>
+  <si>
+    <t>пустую проверку</t>
+  </si>
+  <si>
+    <t>пустой проверка</t>
+  </si>
+  <si>
+    <t>звено закрыто</t>
+  </si>
+  <si>
+    <t>звено закрыт</t>
+  </si>
+  <si>
+    <t>Рукопись следующая</t>
+  </si>
+  <si>
+    <t>Рукопись следующий</t>
+  </si>
+  <si>
+    <t>управлять устройством</t>
+  </si>
+  <si>
+    <t>управлять устройство</t>
+  </si>
+  <si>
+    <t>рукопись, имеющая</t>
+  </si>
+  <si>
+    <t>рукопись имеющий</t>
+  </si>
+  <si>
+    <t>написана рукопись</t>
+  </si>
+  <si>
+    <t>написан рукопись</t>
+  </si>
+  <si>
+    <t>вложенная среда</t>
+  </si>
+  <si>
+    <t>вложенный среда</t>
+  </si>
+  <si>
+    <t>основной рукописи</t>
+  </si>
+  <si>
+    <t>основного рукописи</t>
+  </si>
+  <si>
+    <t>рукопись, выполняющую</t>
+  </si>
+  <si>
+    <t>рукопись выполняющая</t>
+  </si>
+  <si>
+    <t>хранилища рукописей</t>
+  </si>
+  <si>
+    <t>кодовой хранилища</t>
+  </si>
+  <si>
+    <t>ход мыслей который</t>
+  </si>
+  <si>
+    <t>ход мыслей которая</t>
+  </si>
+  <si>
+    <t>случай, в котором</t>
+  </si>
+  <si>
+    <t>случай, в которой</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> о стопке</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> о стопки</t>
+  </si>
+  <si>
+    <t>подходящим решением</t>
+  </si>
+  <si>
+    <t>подходящим соглашением</t>
+  </si>
+  <si>
+    <t>многословное устройство</t>
+  </si>
+  <si>
+    <t>многословную устройство</t>
+  </si>
+  <si>
+    <t>Согласно правил написания</t>
+  </si>
+  <si>
+    <t>Правила написания</t>
+  </si>
+  <si>
+    <t>начало строки</t>
+  </si>
+  <si>
+    <t>остальной ход мыслей</t>
+  </si>
+  <si>
+    <t>остальная ход мыслей</t>
+  </si>
+  <si>
+    <t>жёстко задан</t>
+  </si>
+  <si>
+    <t>жёстко закодирован</t>
+  </si>
+  <si>
+    <t>рукопись была правильной</t>
+  </si>
+  <si>
+    <t>рукопись был правильным</t>
+  </si>
+  <si>
+    <t>вызовет сбой</t>
+  </si>
+  <si>
+    <t>вызовет изъян</t>
+  </si>
+  <si>
+    <t>подобное сочетание</t>
+  </si>
+  <si>
+    <t>подобную сочетание</t>
+  </si>
+  <si>
+    <t>природная особенность</t>
+  </si>
+  <si>
+    <t>природный особенность</t>
+  </si>
+  <si>
+    <t xml:space="preserve">будущие возможности </t>
+  </si>
+  <si>
+    <t xml:space="preserve">будущее возможности </t>
+  </si>
+  <si>
+    <t>собственной мере</t>
+  </si>
+  <si>
+    <t>собственному мере</t>
+  </si>
+  <si>
+    <t>тем  сведениям</t>
+  </si>
+  <si>
+    <t>той  сведениям</t>
+  </si>
+  <si>
+    <t>наибольшее благополучие</t>
+  </si>
+  <si>
+    <t>наибольший благополучие</t>
+  </si>
+  <si>
+    <t>небольшое введение</t>
+  </si>
+  <si>
+    <t>небольшой введение</t>
+  </si>
+  <si>
+    <t>управлять животными позывами</t>
+  </si>
+  <si>
+    <r>
+      <t>управлять</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>животные позывы</t>
+    </r>
+  </si>
+  <si>
+    <t>достоверные сведения</t>
+  </si>
+  <si>
+    <t>достоверная сведения</t>
+  </si>
+  <si>
+    <t xml:space="preserve">то же самое правило </t>
+  </si>
+  <si>
+    <r>
+      <t>та же</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">самая правило </t>
+    </r>
+  </si>
+  <si>
+    <t>семейная казна</t>
+  </si>
+  <si>
+    <t>семейный казна</t>
+  </si>
+  <si>
+    <t>в одинаковом случае</t>
+  </si>
+  <si>
+    <t>в одинаковой случая</t>
+  </si>
+  <si>
+    <t>одно обстоятельство</t>
+  </si>
+  <si>
+    <t>один обстоятельство</t>
+  </si>
+  <si>
+    <t>переносит</t>
+  </si>
+  <si>
+    <t>переносит, переносит</t>
+  </si>
+  <si>
+    <t>ставшая ярлыком</t>
+  </si>
+  <si>
+    <t>ставшая ярлык</t>
+  </si>
+  <si>
+    <t>среду, в которой</t>
+  </si>
+  <si>
+    <t>среду, в котором</t>
+  </si>
+  <si>
+    <t>всё обсуждение</t>
+  </si>
+  <si>
+    <t>вся обсуждение</t>
+  </si>
+  <si>
+    <t>в  воплощении</t>
+  </si>
+  <si>
+    <t>в  воплощения</t>
+  </si>
+  <si>
+    <t>важнейшее значение</t>
+  </si>
+  <si>
+    <t>важнейшую значение</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -257,6 +1126,20 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="204"/>
     </font>
   </fonts>
@@ -280,9 +1163,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -617,7 +1504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08E83B44-291C-467B-924B-0B78C03B23AB}">
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B174"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="28.1796875" customWidth="1"/>
@@ -887,7 +1774,1132 @@
         <v>65</v>
       </c>
     </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A34" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B34" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A35" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A36" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A37" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A38" t="s">
+        <v>74</v>
+      </c>
+      <c r="B38" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A39" t="s">
+        <v>76</v>
+      </c>
+      <c r="B39" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A40" t="s">
+        <v>78</v>
+      </c>
+      <c r="B40" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A41" t="s">
+        <v>80</v>
+      </c>
+      <c r="B41" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A42" t="s">
+        <v>82</v>
+      </c>
+      <c r="B42" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A43" t="s">
+        <v>84</v>
+      </c>
+      <c r="B43" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A44" t="s">
+        <v>85</v>
+      </c>
+      <c r="B44" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A45" t="s">
+        <v>87</v>
+      </c>
+      <c r="B45" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A46" t="s">
+        <v>89</v>
+      </c>
+      <c r="B46" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A47" t="s">
+        <v>91</v>
+      </c>
+      <c r="B47" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A48" t="s">
+        <v>92</v>
+      </c>
+      <c r="B48" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A49" t="s">
+        <v>94</v>
+      </c>
+      <c r="B49" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A50" t="s">
+        <v>96</v>
+      </c>
+      <c r="B50" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A51" t="s">
+        <v>98</v>
+      </c>
+      <c r="B51" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A52" t="s">
+        <v>100</v>
+      </c>
+      <c r="B52" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A53" t="s">
+        <v>102</v>
+      </c>
+      <c r="B53" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A54" t="s">
+        <v>104</v>
+      </c>
+      <c r="B54" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A55" t="s">
+        <v>106</v>
+      </c>
+      <c r="B55" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A56" t="s">
+        <v>108</v>
+      </c>
+      <c r="B56" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A57" t="s">
+        <v>110</v>
+      </c>
+      <c r="B57" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A58" t="s">
+        <v>112</v>
+      </c>
+      <c r="B58" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A59" t="s">
+        <v>114</v>
+      </c>
+      <c r="B59" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A60" t="s">
+        <v>116</v>
+      </c>
+      <c r="B60" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A61" t="s">
+        <v>118</v>
+      </c>
+      <c r="B61" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A62" t="s">
+        <v>120</v>
+      </c>
+      <c r="B62" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A63" t="s">
+        <v>122</v>
+      </c>
+      <c r="B63" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A64" t="s">
+        <v>124</v>
+      </c>
+      <c r="B64" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A65" t="s">
+        <v>126</v>
+      </c>
+      <c r="B65" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A66" t="s">
+        <v>128</v>
+      </c>
+      <c r="B66" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A67" t="s">
+        <v>130</v>
+      </c>
+      <c r="B67" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A68" t="s">
+        <v>132</v>
+      </c>
+      <c r="B68" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A69" t="s">
+        <v>134</v>
+      </c>
+      <c r="B69" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A70" t="s">
+        <v>136</v>
+      </c>
+      <c r="B70" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A71" t="s">
+        <v>138</v>
+      </c>
+      <c r="B71" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A72" t="s">
+        <v>140</v>
+      </c>
+      <c r="B72" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A73" t="s">
+        <v>142</v>
+      </c>
+      <c r="B73" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A74" t="s">
+        <v>144</v>
+      </c>
+      <c r="B74" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A75" t="s">
+        <v>146</v>
+      </c>
+      <c r="B75" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A76" t="s">
+        <v>148</v>
+      </c>
+      <c r="B76" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A77" t="s">
+        <v>150</v>
+      </c>
+      <c r="B77" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A78" t="s">
+        <v>152</v>
+      </c>
+      <c r="B78" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A79" t="s">
+        <v>154</v>
+      </c>
+      <c r="B79" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A80" t="s">
+        <v>156</v>
+      </c>
+      <c r="B80" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A81" t="s">
+        <v>158</v>
+      </c>
+      <c r="B81" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A82" t="s">
+        <v>160</v>
+      </c>
+      <c r="B82" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A83" t="s">
+        <v>162</v>
+      </c>
+      <c r="B83" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A84" t="s">
+        <v>164</v>
+      </c>
+      <c r="B84" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A85" t="s">
+        <v>166</v>
+      </c>
+      <c r="B85" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A86" t="s">
+        <v>168</v>
+      </c>
+      <c r="B86" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A87" t="s">
+        <v>170</v>
+      </c>
+      <c r="B87" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A88" t="s">
+        <v>172</v>
+      </c>
+      <c r="B88" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A89" t="s">
+        <v>174</v>
+      </c>
+      <c r="B89" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A90" t="s">
+        <v>176</v>
+      </c>
+      <c r="B90" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A91" t="s">
+        <v>178</v>
+      </c>
+      <c r="B91" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A92" t="s">
+        <v>180</v>
+      </c>
+      <c r="B92" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A93" t="s">
+        <v>182</v>
+      </c>
+      <c r="B93" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A94" t="s">
+        <v>184</v>
+      </c>
+      <c r="B94" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A95" t="s">
+        <v>186</v>
+      </c>
+      <c r="B95" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A96" t="s">
+        <v>188</v>
+      </c>
+      <c r="B96" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A97" t="s">
+        <v>190</v>
+      </c>
+      <c r="B97" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A98" t="s">
+        <v>192</v>
+      </c>
+      <c r="B98" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A99" t="s">
+        <v>194</v>
+      </c>
+      <c r="B99" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A100" t="s">
+        <v>196</v>
+      </c>
+      <c r="B100" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A101" t="s">
+        <v>198</v>
+      </c>
+      <c r="B101" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A102" t="s">
+        <v>206</v>
+      </c>
+      <c r="B102" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A103" t="s">
+        <v>204</v>
+      </c>
+      <c r="B103" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A104" t="s">
+        <v>202</v>
+      </c>
+      <c r="B104" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A105" t="s">
+        <v>200</v>
+      </c>
+      <c r="B105" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A106" t="s">
+        <v>230</v>
+      </c>
+      <c r="B106" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A107" t="s">
+        <v>228</v>
+      </c>
+      <c r="B107" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A108" t="s">
+        <v>226</v>
+      </c>
+      <c r="B108" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A109" t="s">
+        <v>224</v>
+      </c>
+      <c r="B109" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A110" t="s">
+        <v>222</v>
+      </c>
+      <c r="B110" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A111" t="s">
+        <v>220</v>
+      </c>
+      <c r="B111" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A112" t="s">
+        <v>218</v>
+      </c>
+      <c r="B112" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A113" t="s">
+        <v>216</v>
+      </c>
+      <c r="B113" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A114" t="s">
+        <v>214</v>
+      </c>
+      <c r="B114" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A115" t="s">
+        <v>212</v>
+      </c>
+      <c r="B115" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A116" t="s">
+        <v>210</v>
+      </c>
+      <c r="B116" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A117" t="s">
+        <v>208</v>
+      </c>
+      <c r="B117" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" ht="44.25" x14ac:dyDescent="0.75">
+      <c r="A118" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A119" t="s">
+        <v>248</v>
+      </c>
+      <c r="B119" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A120" t="s">
+        <v>246</v>
+      </c>
+      <c r="B120" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A121" t="s">
+        <v>244</v>
+      </c>
+      <c r="B121" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A122" t="s">
+        <v>242</v>
+      </c>
+      <c r="B122" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A123" t="s">
+        <v>240</v>
+      </c>
+      <c r="B123" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A124" t="s">
+        <v>238</v>
+      </c>
+      <c r="B124" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A125" t="s">
+        <v>236</v>
+      </c>
+      <c r="B125" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A126" t="s">
+        <v>234</v>
+      </c>
+      <c r="B126" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A127" t="s">
+        <v>232</v>
+      </c>
+      <c r="B127" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A128" t="s">
+        <v>270</v>
+      </c>
+      <c r="B128" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A129" t="s">
+        <v>268</v>
+      </c>
+      <c r="B129" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A130" t="s">
+        <v>266</v>
+      </c>
+      <c r="B130" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A131" t="s">
+        <v>264</v>
+      </c>
+      <c r="B131" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A132" t="s">
+        <v>262</v>
+      </c>
+      <c r="B132" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A133" t="s">
+        <v>260</v>
+      </c>
+      <c r="B133" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A134" t="s">
+        <v>258</v>
+      </c>
+      <c r="B134" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A135" t="s">
+        <v>256</v>
+      </c>
+      <c r="B135" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A136" t="s">
+        <v>254</v>
+      </c>
+      <c r="B136" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" ht="44.25" x14ac:dyDescent="0.75">
+      <c r="A137" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A138" t="s">
+        <v>292</v>
+      </c>
+      <c r="B138" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A139" t="s">
+        <v>290</v>
+      </c>
+      <c r="B139" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A140" t="s">
+        <v>288</v>
+      </c>
+      <c r="B140" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A141" t="s">
+        <v>286</v>
+      </c>
+      <c r="B141" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A142" t="s">
+        <v>284</v>
+      </c>
+      <c r="B142" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A143" t="s">
+        <v>282</v>
+      </c>
+      <c r="B143" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A145" t="s">
+        <v>280</v>
+      </c>
+      <c r="B145" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A146" t="s">
+        <v>278</v>
+      </c>
+      <c r="B146" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A147" t="s">
+        <v>276</v>
+      </c>
+      <c r="B147" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A148" t="s">
+        <v>274</v>
+      </c>
+      <c r="B148" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A149" t="s">
+        <v>272</v>
+      </c>
+      <c r="B149" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A150" t="s">
+        <v>293</v>
+      </c>
+      <c r="B150" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A151" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B151" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A152" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B152" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A153" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B153" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A154" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B154" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A155" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="B155" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A156" t="s">
+        <v>303</v>
+      </c>
+      <c r="B156" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A157" t="s">
+        <v>301</v>
+      </c>
+      <c r="B157" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A158" t="s">
+        <v>299</v>
+      </c>
+      <c r="B158" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A159" t="s">
+        <v>297</v>
+      </c>
+      <c r="B159" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A160" t="s">
+        <v>295</v>
+      </c>
+      <c r="B160" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A161" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A162" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B162" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A163" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="B163" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A164" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A165" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B165" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A166" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B166" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A167" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A168" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B168" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A169" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B169" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A170" t="s">
+        <v>333</v>
+      </c>
+      <c r="B170" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A171" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B171" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A172" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B172" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A173" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B173" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.75">
+      <c r="A174" s="2"/>
+      <c r="B174" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3399F58-75D1-4C7B-AB0E-24C152B82179}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/запас словарей/rust.xlsx
+++ b/запас словарей/rust.xlsx
@@ -5,16 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\запас словарей\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA2F6753-0C53-48D8-B491-516154890B80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70566C32-DE4C-4DB7-9C0A-F9738BA4FBD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25710" yWindow="2110" windowWidth="25820" windowHeight="10300" xr2:uid="{FA5CFF00-0E27-4D86-8392-510BBAD6F7FE}"/>
+    <workbookView xWindow="-25710" yWindow="2110" windowWidth="25820" windowHeight="10300" activeTab="1" xr2:uid="{FA5CFF00-0E27-4D86-8392-510BBAD6F7FE}"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
-    <sheet name="Лист2" sheetId="2" r:id="rId2"/>
+    <sheet name="Лист2" sheetId="2" r:id="rId1"/>
+    <sheet name="Лист1" sheetId="1" r:id="rId2"/>
+    <sheet name="Лист3" sheetId="3" r:id="rId3"/>
+    <sheet name="Лист4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="342">
   <si>
     <t>Nightly rust</t>
   </si>
@@ -1106,6 +1108,12 @@
   </si>
   <si>
     <t>важнейшую значение</t>
+  </si>
+  <si>
+    <t>был ли шанс</t>
+  </si>
+  <si>
+    <t>была ли возможность</t>
   </si>
 </sst>
 </file>
@@ -1503,6 +1511,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3399F58-75D1-4C7B-AB0E-24C152B82179}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08E83B44-291C-467B-924B-0B78C03B23AB}">
   <dimension ref="A1:B174"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
@@ -2887,16 +2904,29 @@
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.75">
-      <c r="A174" s="2"/>
-      <c r="B174" s="2"/>
+      <c r="A174" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>341</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3399F58-75D1-4C7B-AB0E-24C152B82179}">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E76D24-AD65-40EA-ACF3-B7DAE43BB5D2}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CFEE5B3-E1BD-4A65-B219-7728B46EDEB0}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData/>
